--- a/final_outputs/figure_b_distribution.xlsx
+++ b/final_outputs/figure_b_distribution.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\international-tax-competitiveness-index\final_outputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DF4B253-4898-4D76-BEFA-AD798742A7D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E453D280-7D5D-4FD5-89AD-47A29C2A2493}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{7939B179-B2E8-475D-84F7-774A10E48CF3}"/>
   </bookViews>
@@ -155,7 +155,7 @@
     <t>Country</t>
   </si>
   <si>
-    <t>Final Score</t>
+    <t>Overall Score</t>
   </si>
 </sst>
 </file>
@@ -171,21 +171,15 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor theme="4" tint="0.79998168889431442"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -193,25 +187,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </top>
-      <bottom style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -288,7 +269,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Final Score</c:v>
+                  <c:v>Overall Score</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -327,25 +308,25 @@
                   <c:v>Luxembourg</c:v>
                 </c:pt>
                 <c:pt idx="6">
+                  <c:v>Czech Republic</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>Australia</c:v>
                 </c:pt>
-                <c:pt idx="7">
-                  <c:v>Czech Republic</c:v>
-                </c:pt>
                 <c:pt idx="8">
+                  <c:v>Turkey</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Hungary</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>Israel</c:v>
                 </c:pt>
-                <c:pt idx="9">
-                  <c:v>Turkey</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>Hungary</c:v>
-                </c:pt>
                 <c:pt idx="11">
+                  <c:v>Slovak Republic</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>Sweden</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>Slovak Republic</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>Costa Rica</c:v>
@@ -369,46 +350,46 @@
                   <c:v>Norway</c:v>
                 </c:pt>
                 <c:pt idx="20">
+                  <c:v>Mexico</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>Finland</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>Greece</c:v>
+                </c:pt>
+                <c:pt idx="23">
                   <c:v>Chile</c:v>
                 </c:pt>
-                <c:pt idx="21">
-                  <c:v>Mexico</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>Finland</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>Greece</c:v>
-                </c:pt>
                 <c:pt idx="24">
+                  <c:v>Slovenia</c:v>
+                </c:pt>
+                <c:pt idx="25">
                   <c:v>Korea</c:v>
                 </c:pt>
-                <c:pt idx="25">
+                <c:pt idx="26">
+                  <c:v>Belgium</c:v>
+                </c:pt>
+                <c:pt idx="27">
                   <c:v>Japan</c:v>
                 </c:pt>
-                <c:pt idx="26">
-                  <c:v>Slovenia</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>Belgium</c:v>
-                </c:pt>
                 <c:pt idx="28">
-                  <c:v>Poland</c:v>
+                  <c:v>Ireland</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>Iceland</c:v>
+                  <c:v>United Kingdom</c:v>
                 </c:pt>
                 <c:pt idx="30">
                   <c:v>Denmark</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>Ireland</c:v>
+                  <c:v>Poland</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>United Kingdom</c:v>
+                  <c:v>Portugal</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>Portugal</c:v>
+                  <c:v>Iceland</c:v>
                 </c:pt>
                 <c:pt idx="34">
                   <c:v>Spain</c:v>
@@ -435,115 +416,115 @@
                   <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>92.478921479331802</c:v>
+                  <c:v>92.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>90.026071776069301</c:v>
+                  <c:v>88.2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>86.775669371845098</c:v>
+                  <c:v>86.8</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>82.553329099630204</c:v>
+                  <c:v>82.6</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>81.903410132011203</c:v>
+                  <c:v>81.900000000000006</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>80.0527199939892</c:v>
+                  <c:v>79.400000000000006</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>79.814996678054001</c:v>
+                  <c:v>78.900000000000006</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>77.645546207861599</c:v>
+                  <c:v>76</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>76.419714036643001</c:v>
+                  <c:v>75.599999999999994</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>76.333261640680902</c:v>
+                  <c:v>75.099999999999994</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>75.597444025541293</c:v>
+                  <c:v>74.7</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>74.7101959668733</c:v>
+                  <c:v>74.599999999999994</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>74.151963588780305</c:v>
+                  <c:v>73.3</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>73.687043974057602</c:v>
+                  <c:v>72.2</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>71.601313881173894</c:v>
+                  <c:v>71.599999999999994</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>71.571353403292804</c:v>
+                  <c:v>71.2</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>70.906301436919406</c:v>
+                  <c:v>70.900000000000006</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>69.198361009133905</c:v>
+                  <c:v>69.2</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>68.048926428257104</c:v>
+                  <c:v>67.5</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>67.221508094223296</c:v>
+                  <c:v>66.900000000000006</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>67.198007694867798</c:v>
+                  <c:v>66.2</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>66.215730326106097</c:v>
+                  <c:v>65.900000000000006</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>65.851998199487198</c:v>
+                  <c:v>65.2</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>64.992270623016296</c:v>
+                  <c:v>64.5</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>64.688298075990204</c:v>
+                  <c:v>63.8</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>64.5499167722474</c:v>
+                  <c:v>63.5</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>63.500136288337202</c:v>
+                  <c:v>62.3</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>63.458745291191299</c:v>
+                  <c:v>62.2</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>63.163904189766001</c:v>
+                  <c:v>61.9</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>62.945740192263898</c:v>
+                  <c:v>61.6</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>62.177908096534601</c:v>
+                  <c:v>61.2</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>60.842437667295698</c:v>
+                  <c:v>59.6</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>59.585475440643997</c:v>
+                  <c:v>59</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>57.524840338337</c:v>
+                  <c:v>57.5</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>50.763076487372302</c:v>
+                  <c:v>50.8</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>49.228990399474398</c:v>
+                  <c:v>47.3</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>45.720921215802797</c:v>
+                  <c:v>45.7</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1309,7 +1290,7 @@
   <autoFilter ref="A1:B39" xr:uid="{0C8726FB-6A84-4EDC-BF2F-88BFE736C5CB}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{E30BF9EF-CB32-4AF6-95C2-7B9B9172AE7E}" name="Country" dataDxfId="1"/>
-    <tableColumn id="2" xr3:uid="{618FC723-9633-4957-99BA-47045360625D}" name="Final Score" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{618FC723-9633-4957-99BA-47045360625D}" name="Overall Score" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1624,307 +1605,307 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2">
         <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A3" s="2" t="s">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2">
-        <v>92.478921479331802</v>
+      <c r="B3">
+        <v>92.5</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="1">
-        <v>90.026071776069301</v>
+      <c r="B4">
+        <v>88.2</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A5" s="2" t="s">
+      <c r="A5" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="2">
-        <v>86.775669371845098</v>
+      <c r="B5">
+        <v>86.8</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="1">
-        <v>82.553329099630204</v>
+      <c r="B6">
+        <v>82.6</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A7" s="2" t="s">
+      <c r="A7" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="2">
-        <v>81.903410132011203</v>
+      <c r="B7">
+        <v>81.900000000000006</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8">
+        <v>79.400000000000006</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="1">
-        <v>80.0527199939892</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A9" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" s="2">
-        <v>79.814996678054001</v>
+      <c r="B9">
+        <v>78.900000000000006</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A10" s="1" t="s">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11">
+        <v>75.599999999999994</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="1">
-        <v>77.645546207861599</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2">
-        <v>76.419714036643001</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A12" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" s="1">
-        <v>76.333261640680902</v>
+      <c r="B12">
+        <v>75.099999999999994</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A13" s="2" t="s">
+      <c r="A13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13">
+        <v>74.7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="2">
-        <v>75.597444025541293</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A14" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B14" s="1">
-        <v>74.7101959668733</v>
+      <c r="B14">
+        <v>74.599999999999994</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A15" s="2" t="s">
+      <c r="A15" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="2">
-        <v>74.151963588780305</v>
+      <c r="B15">
+        <v>73.3</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A16" s="1" t="s">
+      <c r="A16" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="1">
-        <v>73.687043974057602</v>
+      <c r="B16">
+        <v>72.2</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A17" s="2" t="s">
+      <c r="A17" t="s">
         <v>13</v>
       </c>
-      <c r="B17" s="2">
-        <v>71.601313881173894</v>
+      <c r="B17">
+        <v>71.599999999999994</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A18" s="1" t="s">
+      <c r="A18" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="1">
-        <v>71.571353403292804</v>
+      <c r="B18">
+        <v>71.2</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A19" s="2" t="s">
+      <c r="A19" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="2">
-        <v>70.906301436919406</v>
+      <c r="B19">
+        <v>70.900000000000006</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A20" s="1" t="s">
+      <c r="A20" t="s">
         <v>15</v>
       </c>
-      <c r="B20" s="1">
-        <v>69.198361009133905</v>
+      <c r="B20">
+        <v>69.2</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A21" s="2" t="s">
+      <c r="A21" t="s">
         <v>17</v>
       </c>
-      <c r="B21" s="2">
-        <v>68.048926428257104</v>
+      <c r="B21">
+        <v>67.5</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A22" s="1" t="s">
+      <c r="A22" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22">
+        <v>66.900000000000006</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A23" t="s">
+        <v>18</v>
+      </c>
+      <c r="B23">
+        <v>66.2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A24" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24">
+        <v>65.900000000000006</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A25" t="s">
         <v>33</v>
       </c>
-      <c r="B22" s="1">
-        <v>67.221508094223296</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A23" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B23" s="2">
-        <v>67.198007694867798</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A24" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B24" s="1">
-        <v>66.215730326106097</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A25" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B25" s="2">
-        <v>65.851998199487198</v>
+      <c r="B25">
+        <v>65.2</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A26" s="1" t="s">
+      <c r="A26" t="s">
+        <v>16</v>
+      </c>
+      <c r="B26">
+        <v>64.5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A27" t="s">
         <v>22</v>
       </c>
-      <c r="B26" s="1">
-        <v>64.992270623016296</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A27" s="2" t="s">
+      <c r="B27">
+        <v>63.8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A28" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28">
+        <v>63.5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A29" t="s">
         <v>23</v>
       </c>
-      <c r="B27" s="2">
-        <v>64.688298075990204</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A28" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B28" s="1">
-        <v>64.5499167722474</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A29" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B29" s="2">
-        <v>63.500136288337202</v>
+      <c r="B29">
+        <v>62.3</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A30" s="1" t="s">
+      <c r="A30" t="s">
+        <v>27</v>
+      </c>
+      <c r="B30">
+        <v>62.2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A31" t="s">
+        <v>29</v>
+      </c>
+      <c r="B31">
+        <v>61.9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A32" t="s">
+        <v>28</v>
+      </c>
+      <c r="B32">
+        <v>61.6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A33" t="s">
         <v>32</v>
       </c>
-      <c r="B30" s="1">
-        <v>63.458745291191299</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A31" s="2" t="s">
+      <c r="B33">
+        <v>61.2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A34" t="s">
+        <v>35</v>
+      </c>
+      <c r="B34">
+        <v>59.6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A35" t="s">
         <v>31</v>
       </c>
-      <c r="B31" s="2">
-        <v>63.163904189766001</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A32" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B32" s="1">
-        <v>62.945740192263898</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A33" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B33" s="2">
-        <v>62.177908096534601</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A34" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B34" s="1">
-        <v>60.842437667295698</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A35" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B35" s="2">
-        <v>59.585475440643997</v>
+      <c r="B35">
+        <v>59</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A36" s="1" t="s">
+      <c r="A36" t="s">
         <v>30</v>
       </c>
-      <c r="B36" s="1">
-        <v>57.524840338337</v>
+      <c r="B36">
+        <v>57.5</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A37" s="2" t="s">
+      <c r="A37" t="s">
         <v>34</v>
       </c>
-      <c r="B37" s="2">
-        <v>50.763076487372302</v>
+      <c r="B37">
+        <v>50.8</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A38" s="1" t="s">
+      <c r="A38" t="s">
         <v>36</v>
       </c>
-      <c r="B38" s="1">
-        <v>49.228990399474398</v>
+      <c r="B38">
+        <v>47.3</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A39" s="2" t="s">
+      <c r="A39" t="s">
         <v>37</v>
       </c>
-      <c r="B39" s="2">
-        <v>45.720921215802797</v>
+      <c r="B39">
+        <v>45.7</v>
       </c>
     </row>
   </sheetData>
